--- a/tables/miaoyi_log.xlsx
+++ b/tables/miaoyi_log.xlsx
@@ -116,7 +116,7 @@
     <t>12th August 2025</t>
   </si>
   <si>
-    <t>literature review draft reviewing</t>
+    <t xml:space="preserve">reviewed literature review draft </t>
   </si>
   <si>
     <t>20th August 2025</t>
@@ -125,7 +125,7 @@
     <t>finish all and proofreading</t>
   </si>
   <si>
-    <t>22th August 2025</t>
+    <t>22nd August 2025</t>
   </si>
   <si>
     <t>final proofreading</t>
